--- a/timetable_generator/timetable_outputs/ECE_Sem5_SectionA_Timetable.xlsx
+++ b/timetable_generator/timetable_outputs/ECE_Sem5_SectionA_Timetable.xlsx
@@ -466,21 +466,15 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>EC301
-Introduction to VLSI Design
-C101
-Dr. Jagdish D.N</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EC306
-Digital Signal Processing
-C101
-Dr. Sibasankar Padhy</t>
+          <t>HS351
+Happiness &amp; Wellbeing
+C101
+Dr. Chandrika Kamath
+[COMMON]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -492,25 +486,36 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>HS351
-Happiness &amp; Wellbeing
-C101
-Dr. Chandrika Kamath</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>EC306
 Digital Signal Processing
 C101
-Dr. Sibasankar Padhy</t>
-        </is>
-      </c>
+Dr. Sibasankar Padhy
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EC351
+Introduction to Algorithms
+C101
+Dr. Jagdish R.B
+[COMMON]
+[TUTORIAL]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>EC306
+Digital Signal Processing
+C101
+Dr. Sibasankar Padhy
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -518,25 +523,35 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HS351
+Happiness &amp; Wellbeing
+C101
+Dr. Chandrika Kamath
+[COMMON]</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EC351
+Introduction to Algorithms
+C101
+Dr. Jagdish R.B
+[COMMON]</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>EC301
 Introduction to VLSI Design
 C101
-Dr. Jagdish D.N</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>EC306
-Digital Signal Processing
-C101
-Dr. Sibasankar Padhy</t>
-        </is>
-      </c>
+Dr. Jagdish D.N
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -545,31 +560,26 @@
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EC306
+Digital Signal Processing
+C101
+Dr. Sibasankar Padhy
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
         <is>
           <t>EC301
 Introduction to VLSI Design
 C101
-Dr. Jagdish D.N</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>EC351
-Introduction to Algorithms
-C101
-Dr. Jagdish R.B</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>EC351
-Introduction to Algorithms
-C101
-Dr. Jagdish R.B</t>
-        </is>
-      </c>
+Dr. Jagdish D.N
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -577,25 +587,28 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
         <is>
           <t>EC351
 Introduction to Algorithms
 C101
-Dr. Jagdish R.B</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>HS351
-Happiness &amp; Wellbeing
-C101
-Dr. Chandrika Kamath</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+Dr. Jagdish R.B
+[COMMON]</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>EC301
+Introduction to VLSI Design
+C101
+Dr. Jagdish D.N
+[COMMON]
+[TUTORIAL]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
